--- a/doctool/test/auto/scenario28/システム機能設計書_サンプル_S28_expected.xlsx
+++ b/doctool/test/auto/scenario28/システム機能設計書_サンプル_S28_expected.xlsx
@@ -5,12 +5,12 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\PJ\01.Nablarch\repo\review-support-tool\doctool\test\temp_dir\scenario27\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\PJ\01.Nablarch\repo\review-support-tool\doctool\test\temp_dir\scenario28\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7849D09F-C2BE-43CE-8451-0CFE7B4F95AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1E5349C7-9AC9-47D5-ACC3-CBEE49509188}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="780" yWindow="780" windowWidth="38700" windowHeight="15345" tabRatio="822" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3900" yWindow="3900" windowWidth="38700" windowHeight="15345" tabRatio="822" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="エラーシート" sheetId="13" r:id="rId1"/>
@@ -1330,7 +1330,7 @@
     <phoneticPr fontId="13"/>
   </si>
   <si>
-    <t>システム機能設計書_サンプル_S27</t>
+    <t>システム機能設計書_サンプル_S28</t>
   </si>
   <si>
     <t>B5</t>
@@ -3392,7 +3392,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FE2FEC1A-4001-4595-8516-4C9889928A6F}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5D7BFA6D-F3A8-4F79-B8FB-23EBC39F1CD4}">
   <sheetPr codeName="ErrorSheetTemplate">
     <tabColor theme="3" tint="0.59999389629810485"/>
   </sheetPr>
@@ -3452,10 +3452,10 @@
   </sheetData>
   <phoneticPr fontId="10"/>
   <hyperlinks>
-    <hyperlink ref="B3" location="'2. WA1020101(プロジェクト登録画面)'!$E$68" display="'2. WA1020101(プロジェクト登録画面)'!$E$68" xr:uid="{9AC86B1A-32EE-4F6A-8E68-DB745B3AB879}"/>
-    <hyperlink ref="B4" location="'2. WA1020101(プロジェクト登録画面)'!$E$69" display="'2. WA1020101(プロジェクト登録画面)'!$E$69" xr:uid="{6AB6637B-055E-41E9-B9D4-8516F280FB06}"/>
-    <hyperlink ref="B5" location="'2. WA1020101(プロジェクト登録画面)'!$E$70" display="'2. WA1020101(プロジェクト登録画面)'!$E$70" xr:uid="{CA9821EA-3572-4036-9BB9-D1E78D64F171}"/>
-    <hyperlink ref="B6" location="'2. WA1020101(プロジェクト登録画面)'!$E$71" display="'2. WA1020101(プロジェクト登録画面)'!$E$71" xr:uid="{46E85268-46AA-4859-B7C3-7D3448EED91C}"/>
+    <hyperlink ref="B3" location="'2. WA1020101(プロジェクト登録画面)'!$E$68" display="'2. WA1020101(プロジェクト登録画面)'!$E$68" xr:uid="{4521BD8B-22B5-4F21-AA50-E59FD21057E2}"/>
+    <hyperlink ref="B4" location="'2. WA1020101(プロジェクト登録画面)'!$E$69" display="'2. WA1020101(プロジェクト登録画面)'!$E$69" xr:uid="{C72C4843-61DB-404C-80A2-F40F9D9B7DB5}"/>
+    <hyperlink ref="B5" location="'2. WA1020101(プロジェクト登録画面)'!$E$70" display="'2. WA1020101(プロジェクト登録画面)'!$E$70" xr:uid="{911FF07B-BCE3-40E4-9B48-D7B5761EECAF}"/>
+    <hyperlink ref="B6" location="'2. WA1020101(プロジェクト登録画面)'!$E$71" display="'2. WA1020101(プロジェクト登録画面)'!$E$71" xr:uid="{2F8C4466-D9A3-4D93-9594-D062BE681A98}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -3602,7 +3602,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{337D7A6C-C1F6-4E0A-8362-E02258B2A76C}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{763B63FE-1374-40A3-B82A-172AC9F47334}">
   <sheetPr codeName="SheetTemplate">
     <tabColor indexed="44"/>
     <pageSetUpPr fitToPage="1"/>
@@ -4553,19 +4553,19 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="K15:K23" xr:uid="{11769432-BECC-4014-8DB6-3E033225FFFA}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="K15:K23" xr:uid="{D0CF7C5F-FE28-45D2-AEFF-97987FDBCFD6}">
       <formula1>"未,済"</formula1>
     </dataValidation>
   </dataValidations>
   <hyperlinks>
-    <hyperlink ref="B15" location="'2. WA1020101(プロジェクト登録画面)'!$B$5" display="'2. WA1020101(プロジェクト登録画面)'!$B$5" xr:uid="{CFE9EA1F-71AB-4496-BE8D-D886FEA8E782}"/>
-    <hyperlink ref="B16" location="'2. WA1020101(プロジェクト登録画面)'!$E$60" display="'2. WA1020101(プロジェクト登録画面)'!$E$60" xr:uid="{787FF7FE-2CCA-4607-A0C8-4D482459BB1E}"/>
-    <hyperlink ref="B17" location="'2. WA1020101(プロジェクト登録画面)'!$E$62" display="'2. WA1020101(プロジェクト登録画面)'!$E$62" xr:uid="{B3AB575E-DE52-4AEC-B29C-00BC6A754750}"/>
-    <hyperlink ref="B18" location="'2. WA1020101(プロジェクト登録画面)'!$E$63" display="'2. WA1020101(プロジェクト登録画面)'!$E$63" xr:uid="{A1D89FC1-0DBC-4837-B5B4-F16B1387B914}"/>
-    <hyperlink ref="B19" location="'2. WA1020101(プロジェクト登録画面)'!$E$64" display="'2. WA1020101(プロジェクト登録画面)'!$E$64" xr:uid="{BE53EEA4-EA96-4784-8A2F-C1F2D8A5CC11}"/>
-    <hyperlink ref="B20" location="'2. WA1020101(プロジェクト登録画面)'!$E$65" display="'2. WA1020101(プロジェクト登録画面)'!$E$65" xr:uid="{8E0E5D45-00DE-4A5A-8D37-F09A77EA4A84}"/>
-    <hyperlink ref="B21" location="'2. WA1020101(プロジェクト登録画面)'!$E$66" display="'2. WA1020101(プロジェクト登録画面)'!$E$66" xr:uid="{79A40B63-6F21-42D7-AFF1-FC169ABE9B18}"/>
-    <hyperlink ref="B22" location="'2. WA1020101(プロジェクト登録画面)'!$E$67" display="'2. WA1020101(プロジェクト登録画面)'!$E$67" xr:uid="{7364B89F-A372-4F13-9A2D-46542B884BE2}"/>
+    <hyperlink ref="B15" location="'2. WA1020101(プロジェクト登録画面)'!$B$5" display="'2. WA1020101(プロジェクト登録画面)'!$B$5" xr:uid="{22717790-421B-4642-B9F6-DEB03C8B5049}"/>
+    <hyperlink ref="B16" location="'2. WA1020101(プロジェクト登録画面)'!$E$60" display="'2. WA1020101(プロジェクト登録画面)'!$E$60" xr:uid="{CDE13FB3-6723-4095-B8DB-82D6A0144708}"/>
+    <hyperlink ref="B17" location="'2. WA1020101(プロジェクト登録画面)'!$E$62" display="'2. WA1020101(プロジェクト登録画面)'!$E$62" xr:uid="{3E8EDC3A-0270-43E9-BADB-19E954423A73}"/>
+    <hyperlink ref="B18" location="'2. WA1020101(プロジェクト登録画面)'!$E$63" display="'2. WA1020101(プロジェクト登録画面)'!$E$63" xr:uid="{BAB0440D-5FDA-4478-B40E-AE5328F2D74A}"/>
+    <hyperlink ref="B19" location="'2. WA1020101(プロジェクト登録画面)'!$E$64" display="'2. WA1020101(プロジェクト登録画面)'!$E$64" xr:uid="{5C357E34-4D16-4249-968F-5715202E2451}"/>
+    <hyperlink ref="B20" location="'2. WA1020101(プロジェクト登録画面)'!$E$65" display="'2. WA1020101(プロジェクト登録画面)'!$E$65" xr:uid="{3558E812-BDA5-4754-8895-5E58C1072216}"/>
+    <hyperlink ref="B21" location="'2. WA1020101(プロジェクト登録画面)'!$E$66" display="'2. WA1020101(プロジェクト登録画面)'!$E$66" xr:uid="{B0A5978A-E3C0-435C-A298-AA215DB88120}"/>
+    <hyperlink ref="B22" location="'2. WA1020101(プロジェクト登録画面)'!$E$67" display="'2. WA1020101(プロジェクト登録画面)'!$E$67" xr:uid="{8AF2A74F-F094-484F-9BB4-831A15B26B65}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.51200000000000001" footer="0.51200000000000001"/>
   <pageSetup paperSize="9" scale="86" orientation="landscape" verticalDpi="200" r:id="rId1"/>
